--- a/VerveStacks_DEU_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_DEU_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09672501-8FF6-44D1-A267-ECEB96D90E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DABDFED4-F344-40D2-92DA-E0948EC8A50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{8310DF42-1623-447A-84FD-31E7ED9F0748}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8A709263-8FDD-46D7-89B9-AFD66C004B54}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="80">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -68,133 +71,130 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_w1094015892-380_DEU</t>
+    <t>e_DE173-220_DEU</t>
+  </si>
+  <si>
+    <t>e_w870598507_DEU</t>
+  </si>
+  <si>
+    <t>g_DE173-220_DEU-w870598507_DEU</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w108797675-380_DEU-w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w29084374-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w108797675-380_DEU-w29084374-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w952346322-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w108797675-380_DEU-w952346322-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w1128250707-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w1128250707-380_DEU-w108797675-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w275466323_DEU</t>
+  </si>
+  <si>
+    <t>g_w1128250707-380_DEU-w275466323_DEU</t>
+  </si>
+  <si>
+    <t>e_w525964617_DEU</t>
+  </si>
+  <si>
+    <t>g_w1128250707-380_DEU-w525964617_DEU</t>
+  </si>
+  <si>
+    <t>e_w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w143882655-380_DEU-w157328339-380_DEU</t>
+  </si>
+  <si>
+    <t>e_w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w143882655-380_DEU-w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w143882655-380_DEU-w29084374-380_DEU</t>
   </si>
   <si>
     <t>e_w170123812-400_DEU</t>
   </si>
   <si>
-    <t>g_w1094015892-380_DEU-w170123812-400_DEU</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>e_w26472665-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w1094015892-380_DEU-w26472665-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w1128250704-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w1128250704-380_DEU-w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w525964617_DEU</t>
-  </si>
-  <si>
-    <t>g_w1128250704-380_DEU-w525964617_DEU</t>
-  </si>
-  <si>
-    <t>e_w952346322-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w1128250704-380_DEU-w952346322-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w170123812-400_DEU-w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w24757392-380_DEU-w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w24757392-380_DEU-w26472665-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w24757392-380_DEU-w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w24839976-380_DEU-w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w26472665-380_DEU-w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w29309786-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w26472665-380_DEU-w29309786-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w26472665-380_DEU-w525964617_DEU</t>
-  </si>
-  <si>
-    <t>g_w29309786-380_DEU-w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w29309786-380_DEU-w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w29309786-380_DEU-w525964617_DEU</t>
-  </si>
-  <si>
-    <t>e_w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w42410916-380_DEU-w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w42410916-380_DEU-w24839976-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w42410916-380_DEU-w29309786-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w42410916-380_DEU-w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w42488850-380_DEU-w525964617_DEU</t>
-  </si>
-  <si>
-    <t>g_w42488850-380_DEU-w952346322-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w525964617_DEU-w1094015892-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w76246159-380_DEU-w157328339-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w76246159-380_DEU-w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>e_w88916034-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w88916034-380_DEU-w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w88916034-380_DEU-w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>g_w952346322-380_DEU-w24839976-380_DEU</t>
+    <t>g_w157328339-380_DEU-w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>g_w157328339-380_DEU-w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w26472665-380_DEU-w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>g_w275466323_DEU-w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w275466323_DEU-w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w275466323_DEU-w525964617_DEU</t>
+  </si>
+  <si>
+    <t>e_w940919943_DEU</t>
+  </si>
+  <si>
+    <t>g_w275466323_DEU-w940919943_DEU</t>
+  </si>
+  <si>
+    <t>e_DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>g_w29084374-380_DEU-DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>e_w68532663-220_DEU</t>
+  </si>
+  <si>
+    <t>g_w29084374-380_DEU-w68532663-220_DEU</t>
+  </si>
+  <si>
+    <t>e_w449010725-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w449010725-380_DEU-w525964617_DEU</t>
+  </si>
+  <si>
+    <t>g_w68532663-220_DEU-DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>g_w940919943_DEU-w170123812-400_DEU</t>
+  </si>
+  <si>
+    <t>g_w940919943_DEU-w26472665-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w952346322-380_DEU-w1128250707-380_DEU</t>
+  </si>
+  <si>
+    <t>g_w952346322-380_DEU-w870598507_DEU</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -206,88 +206,79 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -63.0 km- way/1094015892-380;way/170123812-400</t>
-  </si>
-  <si>
-    <t>grid link -64.0 km- way/1094015892-380;way/26472665-380</t>
-  </si>
-  <si>
-    <t>grid link -21.0 km- way/1128250704-380;way/42488850-380</t>
-  </si>
-  <si>
-    <t>grid link -42.0 km- way/1128250704-380;way/525964617</t>
-  </si>
-  <si>
-    <t>grid link -27.0 km- way/1128250704-380;way/952346322-380</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- way/157328339-380;way/170123812-400</t>
-  </si>
-  <si>
-    <t>grid link -126.0 km- way/157328339-380;way/24757392-380</t>
-  </si>
-  <si>
-    <t>grid link -117.0 km- way/24757392-380;way/26472665-380</t>
-  </si>
-  <si>
-    <t>grid link -77.0 km- way/24757392-380;way/76246159-380</t>
-  </si>
-  <si>
-    <t>grid link -59.0 km- way/24839976-380;way/42488850-380</t>
-  </si>
-  <si>
-    <t>grid link -139.0 km- way/157328339-380;way/26472665-380</t>
-  </si>
-  <si>
-    <t>grid link -19.0 km- way/26472665-380;way/29309786-380</t>
-  </si>
-  <si>
-    <t>grid link -55.0 km- way/26472665-380;way/525964617</t>
-  </si>
-  <si>
-    <t>grid link -101.0 km- way/24757392-380;way/29309786-380</t>
-  </si>
-  <si>
-    <t>grid link -11.0 km- way/29309786-380;way/42488850-380</t>
-  </si>
-  <si>
-    <t>grid link -63.0 km- way/29309786-380;way/525964617</t>
-  </si>
-  <si>
-    <t>grid link -84.0 km- way/24757392-380;way/42410916-380</t>
-  </si>
-  <si>
-    <t>grid link -41.0 km- way/24839976-380;way/42410916-380</t>
-  </si>
-  <si>
-    <t>grid link -81.0 km- way/29309786-380;way/42410916-380</t>
-  </si>
-  <si>
-    <t>grid link -31.0 km- way/42410916-380;way/42488850-380</t>
-  </si>
-  <si>
-    <t>grid link -17.0 km- way/42488850-380;way/525964617</t>
-  </si>
-  <si>
-    <t>grid link -28.0 km- way/42488850-380;way/952346322-380</t>
-  </si>
-  <si>
-    <t>grid link -99.0 km- way/1094015892-380;way/525964617</t>
-  </si>
-  <si>
-    <t>grid link -50.0 km- way/157328339-380;way/76246159-380</t>
-  </si>
-  <si>
-    <t>grid link -16.0 km- way/42410916-380;way/76246159-380</t>
-  </si>
-  <si>
-    <t>grid link -79.0 km- way/42410916-380;way/88916034-380</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- way/76246159-380;way/88916034-380</t>
-  </si>
-  <si>
-    <t>grid link -20.0 km- way/24839976-380;way/952346322-380</t>
+    <t>grid link -46.0 km- DE173-220;way/870598507</t>
+  </si>
+  <si>
+    <t>grid link -63.0 km- way/108797675-380;way/143882655-380</t>
+  </si>
+  <si>
+    <t>grid link -88.0 km- way/108797675-380;way/29084374-380</t>
+  </si>
+  <si>
+    <t>grid link -18.0 km- way/108797675-380;way/952346322-380</t>
+  </si>
+  <si>
+    <t>grid link -36.0 km- way/108797675-380;way/1128250707-380</t>
+  </si>
+  <si>
+    <t>grid link -51.0 km- way/1128250707-380;way/275466323</t>
+  </si>
+  <si>
+    <t>grid link -62.0 km- way/1128250707-380;way/525964617</t>
+  </si>
+  <si>
+    <t>grid link -98.0 km- way/143882655-380;way/157328339-380</t>
+  </si>
+  <si>
+    <t>grid link -82.0 km- way/143882655-380;way/26472665-380</t>
+  </si>
+  <si>
+    <t>grid link -37.0 km- way/143882655-380;way/29084374-380</t>
+  </si>
+  <si>
+    <t>grid link -42.0 km- way/157328339-380;way/170123812-400</t>
+  </si>
+  <si>
+    <t>grid link -75.0 km- way/157328339-380;way/26472665-380</t>
+  </si>
+  <si>
+    <t>grid link -25.0 km- way/170123812-400;way/26472665-380</t>
+  </si>
+  <si>
+    <t>grid link -22.0 km- way/143882655-380;way/275466323</t>
+  </si>
+  <si>
+    <t>grid link -24.0 km- way/26472665-380;way/275466323</t>
+  </si>
+  <si>
+    <t>grid link -43.0 km- way/275466323;way/525964617</t>
+  </si>
+  <si>
+    <t>grid link -71.0 km- way/275466323;way/940919943</t>
+  </si>
+  <si>
+    <t>grid link -79.0 km- DE206-220;way/29084374-380</t>
+  </si>
+  <si>
+    <t>grid link -68.0 km- way/29084374-380;way/68532663-220</t>
+  </si>
+  <si>
+    <t>grid link -51.0 km- way/449010725-380;way/525964617</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- DE206-220;way/68532663-220</t>
+  </si>
+  <si>
+    <t>grid link -54.0 km- way/170123812-400;way/940919943</t>
+  </si>
+  <si>
+    <t>grid link -30.0 km- way/26472665-380;way/940919943</t>
+  </si>
+  <si>
+    <t>grid link -38.0 km- way/1128250707-380;way/952346322-380</t>
+  </si>
+  <si>
+    <t>grid link -24.0 km- way/870598507;way/952346322-380</t>
   </si>
 </sst>
 </file>
@@ -658,8 +649,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC590746-9B3F-4992-8ABA-A5AAD6EDC114}">
-  <dimension ref="B3:L32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E55EF70-038A-45B3-9139-EC8FBDAB273F}">
+  <dimension ref="B3:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -667,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -693,10 +684,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" t="s">
         <v>54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -725,7 +716,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -739,22 +730,22 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -768,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
@@ -783,7 +774,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -797,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -812,7 +803,7 @@
         <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -826,10 +817,10 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>22</v>
@@ -841,7 +832,7 @@
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -855,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
         <v>23</v>
@@ -870,7 +861,7 @@
         <v>24</v>
       </c>
       <c r="L10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -884,10 +875,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
         <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -899,7 +890,7 @@
         <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -913,22 +904,22 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -942,22 +933,22 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -971,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
@@ -986,7 +977,7 @@
         <v>31</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -1000,22 +991,22 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -1029,10 +1020,10 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
         <v>34</v>
@@ -1044,7 +1035,7 @@
         <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -1058,10 +1049,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>35</v>
@@ -1073,7 +1064,7 @@
         <v>35</v>
       </c>
       <c r="L17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -1087,10 +1078,10 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
@@ -1102,7 +1093,7 @@
         <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -1116,10 +1107,10 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -1131,7 +1122,7 @@
         <v>37</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -1145,10 +1136,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
         <v>38</v>
@@ -1160,7 +1151,7 @@
         <v>38</v>
       </c>
       <c r="L20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -1174,10 +1165,10 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" t="s">
         <v>39</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
       </c>
       <c r="G21" t="s">
         <v>40</v>
@@ -1189,7 +1180,7 @@
         <v>40</v>
       </c>
       <c r="L21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -1203,22 +1194,22 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -1232,22 +1223,22 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -1261,22 +1252,22 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
       <c r="K24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -1290,22 +1281,22 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -1319,22 +1310,22 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -1348,22 +1339,22 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -1377,22 +1368,22 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -1406,109 +1397,22 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" t="s">
-        <v>50</v>
-      </c>
-      <c r="L30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>49</v>
-      </c>
-      <c r="F31" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" t="s">
-        <v>51</v>
-      </c>
-      <c r="L31" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" t="s">
-        <v>52</v>
-      </c>
-      <c r="L32" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
